--- a/Python/Pokemon Sim/dex/data.xlsx
+++ b/Python/Pokemon Sim/dex/data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Pokemon Sim\dex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A538512F-4B71-4FEE-A550-8AABB5564505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9509D2D-FA5C-4601-8297-4023E1062305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{25F1A91D-1B0C-4AC1-B5F5-98D92A2CB783}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{25F1A91D-1B0C-4AC1-B5F5-98D92A2CB783}"/>
   </bookViews>
   <sheets>
     <sheet name="20260610" sheetId="1" r:id="rId1"/>
     <sheet name="20260614" sheetId="2" r:id="rId2"/>
+    <sheet name="20260617" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3165,4 +3166,1704 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF2C1B3-C743-4037-90B2-BF96E735068C}">
+  <dimension ref="A1:A494"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>